--- a/porsche_facilities/Porsche facilities complementar.xlsx
+++ b/porsche_facilities/Porsche facilities complementar.xlsx
@@ -9288,32 +9288,31 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E1077381FFBAFC4BAC7BF913C6116ECA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54a0f8562d4353329dccad99483e7b60">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="481b9579-2565-4348-8a5f-6accbe10b19f" xmlns:ns4="8357f4aa-386c-4c58-b613-10e7f84ba2b7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8ee9209133470b4c9beed2c7abf63c13" ns3:_="" ns4:_="">
-    <xsd:import namespace="481b9579-2565-4348-8a5f-6accbe10b19f"/>
-    <xsd:import namespace="8357f4aa-386c-4c58-b613-10e7f84ba2b7"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010087998874C9DF2A40A49ECA35F11136E5" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="065b27400f0b186c67974d603933646e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fffc50e-d7bf-499b-afc0-146210f27e2b" xmlns:ns3="b778c75e-3458-4d39-94cb-42356e1a46ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa978677c23d0bbf357756e02531e37d" ns2:_="" ns3:_="">
+    <xsd:import namespace="7fffc50e-d7bf-499b-afc0-146210f27e2b"/>
+    <xsd:import namespace="b778c75e-3458-4d39-94cb-42356e1a46ef"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:_activity" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9321,7 +9320,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="481b9579-2565-4348-8a5f-6accbe10b19f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7fffc50e-d7bf-499b-afc0-146210f27e2b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -9334,68 +9333,76 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_activity" ma:index="19" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="12c97838-52bc-4e94-a0f7-48c4b384801d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="22" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8357f4aa-386c-4c58-b613-10e7f84ba2b7" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b778c75e-3458-4d39-94cb-42356e1a46ef" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="10" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{94c55100-5338-4bc1-8430-4f5a34b11e98}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b778c75e-3458-4d39-94cb-42356e1a46ef">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -9414,16 +9421,11 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SharingHintHash" ma:index="12" nillable="true" ma:displayName="Sharing Hint Hash" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9436,8 +9438,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -9529,7 +9531,10 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <_activity xmlns="481b9579-2565-4348-8a5f-6accbe10b19f" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b778c75e-3458-4d39-94cb-42356e1a46ef" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7fffc50e-d7bf-499b-afc0-146210f27e2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
 </file>
@@ -9543,22 +9548,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E199B046-CCCC-4047-A177-A8DC06E71A87}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="481b9579-2565-4348-8a5f-6accbe10b19f"/>
-    <ds:schemaRef ds:uri="8357f4aa-386c-4c58-b613-10e7f84ba2b7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3FB6DA-0BF3-4F12-B183-A54777516577}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
